--- a/docs/實驗參數與批次表_2026-07-18.xlsx
+++ b/docs/實驗參數與批次表_2026-07-18.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2a45ba8d50c0f72c/Desktop/MIRDC/Bioreactor-Edge-AI/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_2B59DBBF95D1D4CC4AADD7B24E3760F56383D824" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DE9F87C-DEDE-46F6-9782-5CEC3522F0D0}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="11_2B59DBBF95D1D4CC4AADD7B24E3760F56383D824" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB5F08A-4022-47C6-AE9A-5173C27456BE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-285" yWindow="795" windowWidth="13733" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="實驗參數與批次表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="70">
   <si>
     <t>生物甲烷化 — 循環時間實驗參數與批次表</t>
   </si>
@@ -95,12 +108,6 @@
   </si>
   <si>
     <t>二、批次排程</t>
-  </si>
-  <si>
-    <t>設定條件</t>
-  </si>
-  <si>
-    <t>量測結果（排氣時填寫）</t>
   </si>
   <si>
     <t>批次
@@ -134,9 +141,6 @@
     <t>pH</t>
   </si>
   <si>
-    <t>ORP</t>
-  </si>
-  <si>
     <t>CH4%
 (排氣峰值)</t>
   </si>
@@ -153,47 +157,109 @@
     <t>0.95~1.0</t>
   </si>
   <si>
-    <t>1.3</t>
-  </si>
-  <si>
     <t>2.1</t>
   </si>
   <si>
     <t>5 分</t>
   </si>
   <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>2.3</t>
-  </si>
-  <si>
     <t>3.1</t>
   </si>
   <si>
     <t>10 分</t>
   </si>
   <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t>※ 每個循環時間重複 3 次（比照 1.1/1.2/1.3 編號）；量測欄位於實驗時填寫。</t>
-  </si>
-  <si>
-    <t>※ 待與洪博討論：循環時間水準是否合適、是否需再加其他因子。</t>
-  </si>
-  <si>
-    <t>2026-07-18　李承育</t>
+    <t>2026-07-27　李承育</t>
+  </si>
+  <si>
+    <t>混和槽壓力</t>
+  </si>
+  <si>
+    <t>反應槽壓力</t>
+  </si>
+  <si>
+    <t>CO2%</t>
+  </si>
+  <si>
+    <t>ORP (mv)</t>
+  </si>
+  <si>
+    <t>量測結果（進氣後基準值 )</t>
+  </si>
+  <si>
+    <t>CH4%
+(洗管線後)</t>
+  </si>
+  <si>
+    <t>量測結果（進氣前基準值 )</t>
+  </si>
+  <si>
+    <t>設定條件 (進氣後及排氣後)</t>
+  </si>
+  <si>
+    <t>設定條件 (進氣前及排氣前)</t>
+  </si>
+  <si>
+    <t>量測結果（排氣前）</t>
+  </si>
+  <si>
+    <t>循環時間c
+(每時幾分)</t>
+  </si>
+  <si>
+    <t>時間戳</t>
+  </si>
+  <si>
+    <t>CH4%</t>
+  </si>
+  <si>
+    <t>31.64% (目測)</t>
+  </si>
+  <si>
+    <t>2026/07/27                          09:17:43上午</t>
+  </si>
+  <si>
+    <t>2026/07/22  14:44:06下午</t>
+  </si>
+  <si>
+    <t>2026/07/22  14:48:37下午</t>
+  </si>
+  <si>
+    <t>2026/7/27  09:18:04上午</t>
+  </si>
+  <si>
+    <t>三、批次排程</t>
+  </si>
+  <si>
+    <t>觀察現象補充</t>
+  </si>
+  <si>
+    <t>CO2% (排氣峰值)</t>
+  </si>
+  <si>
+    <t>量測結果（排氣後當下峰值）</t>
+  </si>
+  <si>
+    <t>21% (目測)</t>
+  </si>
+  <si>
+    <t>排氣中</t>
+  </si>
+  <si>
+    <t>觀察到排氣時 ORP (mv) 往上升，pH值會往鹼性 ( 6.96 -&gt; 7.00) 後大致經過 5min 趨緩後 ( 7.00 -&gt; 6.96) ，ORP 也一併向下，後又開始震盪。</t>
+  </si>
+  <si>
+    <t>2026/7/27  09:25:13上午</t>
+  </si>
+  <si>
+    <t>無</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,8 +299,32 @@
       <sz val="11"/>
       <name val="微軟正黑體"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微軟"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,8 +351,32 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -309,11 +423,209 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -337,17 +649,163 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -363,6 +821,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,21 +1112,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.3984375" customWidth="1"/>
     <col min="2" max="2" width="20.9296875" customWidth="1"/>
-    <col min="3" max="4" width="32.73046875" customWidth="1"/>
+    <col min="3" max="3" width="32.73046875" customWidth="1"/>
+    <col min="4" max="4" width="34.46484375" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="7.53125" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" customWidth="1"/>
+    <col min="11" max="11" width="11.265625" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="14" width="12.59765625" customWidth="1"/>
+    <col min="15" max="15" width="12.1328125" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="14.1328125" customWidth="1"/>
+    <col min="21" max="21" width="15.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:21" ht="24" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10"/>
@@ -675,9 +1149,9 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="9" t="s">
-        <v>52</v>
+    <row r="2" spans="1:21">
+      <c r="A2" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -687,12 +1161,12 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="4" spans="1:10" ht="15.4">
+    <row r="4" spans="1:21" ht="15.4">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:21">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -706,7 +1180,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="21.75" customHeight="1">
+    <row r="6" spans="1:21" ht="21.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -720,7 +1194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.149999999999999" customHeight="1">
+    <row r="7" spans="1:21" ht="19.149999999999999" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -734,7 +1208,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="20.65" customHeight="1">
+    <row r="8" spans="1:21" ht="20.65" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -748,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="19.899999999999999" customHeight="1">
+    <row r="9" spans="1:21" ht="19.899999999999999" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -762,7 +1236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="23.65" customHeight="1">
+    <row r="10" spans="1:21" ht="23.65" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
@@ -776,8 +1250,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:21">
+      <c r="A12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="10"/>
@@ -788,82 +1262,169 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="14" spans="1:10" ht="15.4">
+    <row r="14" spans="1:21" ht="15.4">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20" customHeight="1">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:21" ht="20" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="33"/>
+    </row>
+    <row r="16" spans="1:21" ht="34.049999999999997" customHeight="1">
+      <c r="A16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="11" t="s">
+      <c r="B16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" ht="34.049999999999997" customHeight="1">
-      <c r="A16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="F16" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="P16" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="Q16" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="R16" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="T16" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="U16" s="37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="42.75" customHeight="1">
+      <c r="A17" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10">
+        <v>37</v>
+      </c>
+      <c r="F17" s="8">
+        <v>2.4990000000000001</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="H17" s="8">
+        <v>7.01</v>
+      </c>
+      <c r="I17" s="8">
+        <v>516</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="K17" s="19">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L17" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="47">
+        <v>3.1640000000000001</v>
+      </c>
+      <c r="N17" s="47">
+        <v>1.085</v>
+      </c>
+      <c r="O17" s="47">
+        <v>114.485</v>
+      </c>
+      <c r="P17" s="47"/>
+      <c r="Q17" s="47">
+        <v>6.97</v>
+      </c>
+      <c r="R17" s="47">
+        <v>585</v>
+      </c>
+      <c r="S17" s="56">
+        <v>0</v>
+      </c>
+      <c r="T17" s="57">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="U17" s="38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="39" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
@@ -871,211 +1432,461 @@
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
+      <c r="U18" s="14"/>
+    </row>
+    <row r="19" spans="1:21" ht="44.25" customHeight="1">
+      <c r="A19" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="J19" s="12"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+    </row>
+    <row r="20" spans="1:21" ht="22.9" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="50"/>
+    </row>
+    <row r="21" spans="1:21" ht="43.5" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="3" t="s">
+      <c r="G21" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="H21" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="N21" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="T21" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="U21" s="55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="49.15" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="8">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1.179</v>
+      </c>
+      <c r="H22" s="8">
+        <v>7.02</v>
+      </c>
+      <c r="I22" s="8">
+        <v>502</v>
+      </c>
+      <c r="J22" s="18">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="K22" s="19">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L22" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="47">
+        <v>3.16</v>
+      </c>
+      <c r="N22" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q22" s="47">
+        <v>6.97</v>
+      </c>
+      <c r="R22" s="47">
+        <v>586</v>
+      </c>
+      <c r="S22" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="T22" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="U22" s="38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="42" customHeight="1">
+      <c r="A23" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="8">
+        <v>1.7809999999999999</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1.1910000000000001</v>
+      </c>
+      <c r="H23" s="8">
+        <v>6.99</v>
+      </c>
+      <c r="I23" s="8">
+        <v>533</v>
+      </c>
+      <c r="J23" s="18">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="K23" s="19">
+        <v>8.5599999999999996E-2</v>
+      </c>
+      <c r="L23" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="45"/>
+      <c r="U23" s="45"/>
+    </row>
+    <row r="24" spans="1:21" ht="46.5" customHeight="1">
+      <c r="A24" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="J24" s="12"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45"/>
+    </row>
+    <row r="27" spans="1:21" ht="15.4">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="48.75" customHeight="1">
+      <c r="A28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+    </row>
+    <row r="29" spans="1:21" ht="42.4" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="63"/>
+    </row>
+    <row r="30" spans="1:21" ht="43.9" customHeight="1">
+      <c r="A30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="B30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="61"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="62"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="63"/>
+    </row>
+    <row r="31" spans="1:21" ht="48.4" customHeight="1">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="B31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="F28:R28"/>
+    <mergeCell ref="F29:R29"/>
+    <mergeCell ref="F30:R30"/>
+    <mergeCell ref="F31:R31"/>
+    <mergeCell ref="F20:L20"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="F15:J15"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="F15:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
